--- a/survey_templates/045_staff_golf_season_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/045_staff_golf_season_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1279,17 +1279,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>suggestions_for_future_programs_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Very Positive</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>very_positive</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Very Positive</t>
+          <t>Somewhat Positive</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>somewhat_positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Somewhat Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Negative</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>somewhat_negative</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Somewhat Negative</t>
+          <t>Very Negative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>would_participate_again_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_negative</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very Negative</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>would_participate_again_choices</t>
+          <t>staff_support_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>staff_support_choices</t>
+          <t>event_organizer_support_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>event_organizer_support_choices</t>
+          <t>staff_satisfaction_rating2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>staff_satisfaction_rating2_choices</t>
+          <t>suggestions_for_future_tournaments_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>improve_golf_tournament_duration</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Improve golf tournament duration</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>improve_golf_tournament_duration</t>
+          <t>increase_golf_tournament_budget</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Improve golf tournament duration</t>
+          <t>Increase golf tournament budget</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>increase_golf_tournament_budget</t>
+          <t>better_golf_tournament_location</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Increase golf tournament budget</t>
+          <t>Better golf tournament location</t>
         </is>
       </c>
     </row>
@@ -1709,46 +1709,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>better_golf_tournament_location</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Better golf tournament location</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>suggestions_for_future_tournaments_choices</t>
+          <t>staff_suggestions_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>improve_staff_support</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Improve staff support</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>suggestions_for_future_tournaments_choices</t>
+          <t>staff_suggestions_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>increase_staff_training</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Increase staff training</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>improve_staff_support</t>
+          <t>better_staff_location</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Improve staff support</t>
+          <t>Better staff location</t>
         </is>
       </c>
     </row>
@@ -1777,63 +1777,63 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>increase_staff_training</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Increase staff training</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>staff_suggestions_choices</t>
+          <t>overall_experience2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>better_staff_location</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Better staff location</t>
+          <t>Very Positive</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>staff_suggestions_choices</t>
+          <t>overall_experience2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat Positive</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>staff_suggestions_choices</t>
+          <t>overall_experience2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>very_positive</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Very Positive</t>
+          <t>Somewhat Negative</t>
         </is>
       </c>
     </row>
@@ -1862,63 +1862,63 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>somewhat_positive</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Somewhat Positive</t>
+          <t>Very Negative</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>overall_experience2_choices</t>
+          <t>staff_satisfaction_rating3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>overall_experience2_choices</t>
+          <t>staff_satisfaction_rating3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>somewhat_negative</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Somewhat Negative</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>overall_experience2_choices</t>
+          <t>staff_satisfaction_rating3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>very_negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Very Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1947,61 +1947,10 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
-        <is>
-          <t>Somewhat Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_rating3_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_rating3_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>somewhat_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Somewhat Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_rating3_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
         <is>
           <t>Very Dissatisfied</t>
         </is>
